--- a/hu_OEVK_2026.xlsx
+++ b/hu_OEVK_2026.xlsx
@@ -753,7 +753,7 @@
         <v>49</v>
       </c>
       <c r="G7" s="13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H7" s="5" t="n">
         <v>9</v>
